--- a/artfynd/A 32960-2019 artfynd.xlsx
+++ b/artfynd/A 32960-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32960-2019 artfynd.xlsx
+++ b/artfynd/A 32960-2019 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121367205</v>
+        <v>121364498</v>
       </c>
       <c r="B12" t="n">
-        <v>97991</v>
+        <v>98744</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,23 +1747,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223597</v>
+        <v>222322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1834,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121364498</v>
+        <v>121367205</v>
       </c>
       <c r="B13" t="n">
-        <v>98744</v>
+        <v>97991</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,27 +1850,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222322</v>
+        <v>223597</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>DC.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>

--- a/artfynd/A 32960-2019 artfynd.xlsx
+++ b/artfynd/A 32960-2019 artfynd.xlsx
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121369521</v>
+        <v>121364498</v>
       </c>
       <c r="B10" t="n">
-        <v>98105</v>
+        <v>98754</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,25 +1541,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>222322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
         <v>121367014</v>
       </c>
       <c r="B11" t="n">
-        <v>98046</v>
+        <v>98056</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121364498</v>
+        <v>121369521</v>
       </c>
       <c r="B12" t="n">
-        <v>98744</v>
+        <v>98115</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222322</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,7 +1841,7 @@
         <v>121367205</v>
       </c>
       <c r="B13" t="n">
-        <v>97991</v>
+        <v>98001</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 32960-2019 artfynd.xlsx
+++ b/artfynd/A 32960-2019 artfynd.xlsx
@@ -1632,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121367014</v>
+        <v>121367205</v>
       </c>
       <c r="B11" t="n">
-        <v>98056</v>
+        <v>98001</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,23 +1648,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219797</v>
+        <v>223597</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1838,10 +1834,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121367205</v>
+        <v>121367014</v>
       </c>
       <c r="B13" t="n">
-        <v>98001</v>
+        <v>98056</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,19 +1850,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223597</v>
+        <v>219797</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>

--- a/artfynd/A 32960-2019 artfynd.xlsx
+++ b/artfynd/A 32960-2019 artfynd.xlsx
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121364498</v>
+        <v>121367205</v>
       </c>
       <c r="B10" t="n">
-        <v>98754</v>
+        <v>98014</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,27 +1541,23 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222322</v>
+        <v>223597</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>DC.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1632,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121367205</v>
+        <v>121369521</v>
       </c>
       <c r="B11" t="n">
-        <v>98001</v>
+        <v>98128</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,19 +1644,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223597</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121369521</v>
+        <v>121367014</v>
       </c>
       <c r="B12" t="n">
-        <v>98115</v>
+        <v>98069</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,21 +1747,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>219797</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121367014</v>
+        <v>121364498</v>
       </c>
       <c r="B13" t="n">
-        <v>98056</v>
+        <v>98767</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,25 +1846,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219797</v>
+        <v>222322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 32960-2019 artfynd.xlsx
+++ b/artfynd/A 32960-2019 artfynd.xlsx
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121367205</v>
+        <v>121367014</v>
       </c>
       <c r="B10" t="n">
-        <v>98014</v>
+        <v>98070</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,19 +1545,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223597</v>
+        <v>219797</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1628,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121369521</v>
+        <v>121367205</v>
       </c>
       <c r="B11" t="n">
-        <v>98128</v>
+        <v>98015</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,23 +1648,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>223597</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121367014</v>
+        <v>121369521</v>
       </c>
       <c r="B12" t="n">
-        <v>98069</v>
+        <v>98129</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,21 +1747,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219797</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1837,7 +1837,7 @@
         <v>121364498</v>
       </c>
       <c r="B13" t="n">
-        <v>98767</v>
+        <v>98768</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 32960-2019 artfynd.xlsx
+++ b/artfynd/A 32960-2019 artfynd.xlsx
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121367014</v>
+        <v>121367205</v>
       </c>
       <c r="B10" t="n">
-        <v>98070</v>
+        <v>98018</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,23 +1545,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219797</v>
+        <v>223597</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1632,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121367205</v>
+        <v>121367014</v>
       </c>
       <c r="B11" t="n">
-        <v>98015</v>
+        <v>98073</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,19 +1644,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223597</v>
+        <v>219797</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121369521</v>
+        <v>121364498</v>
       </c>
       <c r="B12" t="n">
-        <v>98129</v>
+        <v>98771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,25 +1743,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>222322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121364498</v>
+        <v>121369521</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>98132</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,25 +1846,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222322</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 32960-2019 artfynd.xlsx
+++ b/artfynd/A 32960-2019 artfynd.xlsx
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121367205</v>
+        <v>121367014</v>
       </c>
       <c r="B10" t="n">
-        <v>98018</v>
+        <v>98073</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,19 +1545,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223597</v>
+        <v>219797</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1628,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121367014</v>
+        <v>121367205</v>
       </c>
       <c r="B11" t="n">
-        <v>98073</v>
+        <v>98018</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,23 +1648,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219797</v>
+        <v>223597</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121364498</v>
+        <v>121369521</v>
       </c>
       <c r="B12" t="n">
-        <v>98771</v>
+        <v>98132</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,25 +1743,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222322</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121369521</v>
+        <v>121364498</v>
       </c>
       <c r="B13" t="n">
-        <v>98132</v>
+        <v>98771</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,25 +1846,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>222322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 32960-2019 artfynd.xlsx
+++ b/artfynd/A 32960-2019 artfynd.xlsx
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121367014</v>
+        <v>121367205</v>
       </c>
       <c r="B10" t="n">
-        <v>98073</v>
+        <v>98024</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,23 +1545,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219797</v>
+        <v>223597</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1632,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121367205</v>
+        <v>121364498</v>
       </c>
       <c r="B11" t="n">
-        <v>98018</v>
+        <v>98777</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,23 +1640,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223597</v>
+        <v>222322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121369521</v>
+        <v>121367014</v>
       </c>
       <c r="B12" t="n">
-        <v>98132</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,21 +1747,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>219797</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121364498</v>
+        <v>121369521</v>
       </c>
       <c r="B13" t="n">
-        <v>98771</v>
+        <v>98138</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,25 +1846,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222322</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 32960-2019 artfynd.xlsx
+++ b/artfynd/A 32960-2019 artfynd.xlsx
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121367205</v>
+        <v>121369521</v>
       </c>
       <c r="B10" t="n">
-        <v>98024</v>
+        <v>98139</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,19 +1545,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223597</v>
+        <v>219874</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1628,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121364498</v>
+        <v>121367014</v>
       </c>
       <c r="B11" t="n">
-        <v>98777</v>
+        <v>98080</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1640,25 +1644,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222322</v>
+        <v>219797</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121367014</v>
+        <v>121367205</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>98025</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,23 +1751,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219797</v>
+        <v>223597</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1834,10 +1834,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121369521</v>
+        <v>121364498</v>
       </c>
       <c r="B13" t="n">
-        <v>98138</v>
+        <v>98778</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,25 +1846,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>222322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/artfynd/A 32960-2019 artfynd.xlsx
+++ b/artfynd/A 32960-2019 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121367205</v>
+        <v>121364498</v>
       </c>
       <c r="B12" t="n">
-        <v>98025</v>
+        <v>98778</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,23 +1747,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223597</v>
+        <v>222322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1834,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121364498</v>
+        <v>121367205</v>
       </c>
       <c r="B13" t="n">
-        <v>98778</v>
+        <v>98025</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,27 +1850,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222322</v>
+        <v>223597</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>DC.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>

--- a/artfynd/A 32960-2019 artfynd.xlsx
+++ b/artfynd/A 32960-2019 artfynd.xlsx
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121369521</v>
+        <v>121364498</v>
       </c>
       <c r="B10" t="n">
-        <v>98139</v>
+        <v>98778</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,25 +1541,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>222322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121367014</v>
+        <v>121369521</v>
       </c>
       <c r="B11" t="n">
-        <v>98080</v>
+        <v>98139</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,21 +1648,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219797</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121364498</v>
+        <v>121367014</v>
       </c>
       <c r="B12" t="n">
-        <v>98778</v>
+        <v>98080</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222322</v>
+        <v>219797</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>

--- a/artfynd/A 32960-2019 artfynd.xlsx
+++ b/artfynd/A 32960-2019 artfynd.xlsx
@@ -1529,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121364498</v>
+        <v>121369521</v>
       </c>
       <c r="B10" t="n">
-        <v>98778</v>
+        <v>98139</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,25 +1541,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222322</v>
+        <v>219874</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121369521</v>
+        <v>121367014</v>
       </c>
       <c r="B11" t="n">
-        <v>98139</v>
+        <v>98080</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,21 +1648,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>219797</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hoffm.) Besser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121367014</v>
+        <v>121367205</v>
       </c>
       <c r="B12" t="n">
-        <v>98080</v>
+        <v>98025</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,23 +1751,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219797</v>
+        <v>223597</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1838,10 +1834,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121367205</v>
+        <v>121364498</v>
       </c>
       <c r="B13" t="n">
-        <v>98025</v>
+        <v>98778</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1850,23 +1846,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223597</v>
+        <v>222322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
